--- a/timecamp/TimeCamp Time Report.xlsx
+++ b/timecamp/TimeCamp Time Report.xlsx
@@ -11,14 +11,14 @@
     <sheet name="Time Tracking Report - decimal" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TimeCamp Time Report'!$B$6:$H$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TimeCamp Time Report'!$B$6:$H$31</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="63">
   <si>
     <t>Time frame</t>
   </si>
@@ -38,7 +38,7 @@
     <t>2026-03-31</t>
   </si>
   <si>
-    <t>2026-03-18 11:50:44</t>
+    <t>2026-03-12 04:02:15</t>
   </si>
   <si>
     <t>Projects</t>
@@ -80,10 +80,10 @@
     <t>Total</t>
   </si>
   <si>
-    <t>15h 11m</t>
-  </si>
-  <si>
-    <t>2026-03-18</t>
+    <t>11h 32m</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
   </si>
   <si>
     <t>ekrivonogov</t>
@@ -92,118 +92,70 @@
     <t>SQL</t>
   </si>
   <si>
-    <t>1h 18m</t>
-  </si>
-  <si>
-    <t>9:26-10:54</t>
+    <t>1h 01m</t>
+  </si>
+  <si>
+    <t>2:59-4:00</t>
   </si>
   <si>
     <t>Data Engineer</t>
   </si>
   <si>
-    <t>30m</t>
-  </si>
-  <si>
-    <t>11:16-11:46</t>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>34m</t>
+  </si>
+  <si>
+    <t>6:10-6:49</t>
+  </si>
+  <si>
+    <t>23m</t>
+  </si>
+  <si>
+    <t>15:19-15:43</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>37m</t>
+  </si>
+  <si>
+    <t>17:25-18:02</t>
   </si>
   <si>
     <t>25m</t>
   </si>
   <si>
-    <t>7:23-7:48</t>
-  </si>
-  <si>
-    <t>0s</t>
-  </si>
-  <si>
-    <t>8:06-8:06</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>1h 17m</t>
-  </si>
-  <si>
-    <t>13:29-14:57</t>
-  </si>
-  <si>
-    <t>03m</t>
-  </si>
-  <si>
-    <t>16:44-16:47</t>
+    <t>5:39-6:05</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>56m</t>
+  </si>
+  <si>
+    <t>5:04-6:03</t>
+  </si>
+  <si>
+    <t>3:52-4:51</t>
+  </si>
+  <si>
+    <t>24m</t>
+  </si>
+  <si>
+    <t>17:33-17:58</t>
+  </si>
+  <si>
+    <t>09m</t>
+  </si>
+  <si>
+    <t>18:14-18:26</t>
   </si>
   <si>
     <t>02m</t>
-  </si>
-  <si>
-    <t>17:05-17:10</t>
-  </si>
-  <si>
-    <t>01m</t>
-  </si>
-  <si>
-    <t>17:23-17:24</t>
-  </si>
-  <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
-    <t>1h 01m</t>
-  </si>
-  <si>
-    <t>2:59-4:00</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
-    <t>34m</t>
-  </si>
-  <si>
-    <t>6:10-6:49</t>
-  </si>
-  <si>
-    <t>23m</t>
-  </si>
-  <si>
-    <t>15:19-15:43</t>
-  </si>
-  <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
-    <t>37m</t>
-  </si>
-  <si>
-    <t>17:25-18:02</t>
-  </si>
-  <si>
-    <t>5:39-6:05</t>
-  </si>
-  <si>
-    <t>2026-03-04</t>
-  </si>
-  <si>
-    <t>56m</t>
-  </si>
-  <si>
-    <t>5:04-6:03</t>
-  </si>
-  <si>
-    <t>3:52-4:51</t>
-  </si>
-  <si>
-    <t>24m</t>
-  </si>
-  <si>
-    <t>17:33-17:58</t>
-  </si>
-  <si>
-    <t>09m</t>
-  </si>
-  <si>
-    <t>18:14-18:26</t>
   </si>
   <si>
     <t>17:09-17:11</t>
@@ -911,7 +863,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="9.10" bestFit="true" style="0"/>
@@ -1029,7 +981,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>22</v>
@@ -1038,10 +990,10 @@
         <v>23</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="16" t="s">
@@ -1050,7 +1002,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="B10" s="19" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>22</v>
@@ -1059,10 +1011,10 @@
         <v>23</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10" s="22"/>
       <c r="H10" s="16" t="s">
@@ -1071,7 +1023,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="B11" s="19" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>22</v>
@@ -1080,10 +1032,10 @@
         <v>23</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G11" s="22"/>
       <c r="H11" s="16" t="s">
@@ -1092,7 +1044,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>22</v>
@@ -1101,10 +1053,10 @@
         <v>23</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" s="22"/>
       <c r="H12" s="16" t="s">
@@ -1113,7 +1065,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="B13" s="19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C13" s="21" t="s">
         <v>22</v>
@@ -1122,10 +1074,10 @@
         <v>23</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G13" s="22"/>
       <c r="H13" s="16" t="s">
@@ -1134,7 +1086,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="B14" s="19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>22</v>
@@ -1146,7 +1098,7 @@
         <v>38</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G14" s="22"/>
       <c r="H14" s="16" t="s">
@@ -1155,7 +1107,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="B15" s="19" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C15" s="21" t="s">
         <v>22</v>
@@ -1164,10 +1116,10 @@
         <v>23</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G15" s="22"/>
       <c r="H15" s="16" t="s">
@@ -1176,7 +1128,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="B16" s="19" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C16" s="21" t="s">
         <v>22</v>
@@ -1197,19 +1149,19 @@
     </row>
     <row r="17" spans="1:8">
       <c r="B17" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="23" t="s">
+      <c r="F17" s="21" t="s">
         <v>46</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>47</v>
       </c>
       <c r="G17" s="22"/>
       <c r="H17" s="16" t="s">
@@ -1218,7 +1170,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="B18" s="19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" s="21" t="s">
         <v>22</v>
@@ -1239,19 +1191,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="B19" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="23" t="s">
+      <c r="F19" s="21" t="s">
         <v>51</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>52</v>
       </c>
       <c r="G19" s="22"/>
       <c r="H19" s="16" t="s">
@@ -1260,7 +1212,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="B20" s="19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" s="21" t="s">
         <v>22</v>
@@ -1269,10 +1221,10 @@
         <v>23</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" s="22"/>
       <c r="H20" s="16" t="s">
@@ -1281,7 +1233,7 @@
     </row>
     <row r="21" spans="1:8">
       <c r="B21" s="19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C21" s="21" t="s">
         <v>22</v>
@@ -1302,7 +1254,7 @@
     </row>
     <row r="22" spans="1:8">
       <c r="B22" s="19" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>22</v>
@@ -1311,10 +1263,10 @@
         <v>23</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G22" s="22"/>
       <c r="H22" s="16" t="s">
@@ -1323,7 +1275,7 @@
     </row>
     <row r="23" spans="1:8">
       <c r="B23" s="19" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="C23" s="21" t="s">
         <v>22</v>
@@ -1332,10 +1284,10 @@
         <v>23</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G23" s="22"/>
       <c r="H23" s="16" t="s">
@@ -1344,7 +1296,7 @@
     </row>
     <row r="24" spans="1:8">
       <c r="B24" s="19" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="C24" s="21" t="s">
         <v>22</v>
@@ -1353,10 +1305,10 @@
         <v>23</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G24" s="22"/>
       <c r="H24" s="16" t="s">
@@ -1364,188 +1316,20 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="B25" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" s="22"/>
-      <c r="H25" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="B26" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26" s="22"/>
-      <c r="H26" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="B27" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="22"/>
-      <c r="H27" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="B28" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="F28" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="22"/>
-      <c r="H28" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="B29" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" s="22"/>
-      <c r="H29" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="B30" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G30" s="22"/>
-      <c r="H30" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="B31" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="22"/>
-      <c r="H31" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="B32" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G32" s="22"/>
-      <c r="H32" s="16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="B33" s="29" t="s">
+      <c r="B25" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="25" t="s">
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="28"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="28"/>
     </row>
   </sheetData>
-  <autoFilter ref="B6:H39"/>
+  <autoFilter ref="B6:H31"/>
   <mergeCells>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C4:D4"/>
@@ -1561,7 +1345,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
@@ -1608,7 +1392,7 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>15.19</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -1622,7 +1406,7 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="E3" t="s">
         <v>25</v>
@@ -1633,7 +1417,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1642,10 +1426,10 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
         <v>26</v>
@@ -1653,7 +1437,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -1662,10 +1446,10 @@
         <v>23</v>
       </c>
       <c r="D5">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -1673,7 +1457,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -1682,10 +1466,10 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>0.0</v>
+        <v>0.62</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
         <v>26</v>
@@ -1693,7 +1477,7 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
@@ -1702,10 +1486,10 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>1.3</v>
+        <v>0.43</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
         <v>26</v>
@@ -1713,7 +1497,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
@@ -1722,10 +1506,10 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>0.06</v>
+        <v>0.94</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G8" t="s">
         <v>26</v>
@@ -1733,7 +1517,7 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -1742,10 +1526,10 @@
         <v>23</v>
       </c>
       <c r="D9">
-        <v>0.04</v>
+        <v>0.93</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
         <v>26</v>
@@ -1753,7 +1537,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
@@ -1762,10 +1546,10 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>0.02</v>
+        <v>0.4</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
         <v>26</v>
@@ -1773,7 +1557,7 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
         <v>22</v>
@@ -1782,7 +1566,7 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>1.02</v>
+        <v>0.17</v>
       </c>
       <c r="E11" t="s">
         <v>44</v>
@@ -1793,7 +1577,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
@@ -1802,10 +1586,10 @@
         <v>23</v>
       </c>
       <c r="D12">
-        <v>0.58</v>
+        <v>0.03</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" t="s">
         <v>26</v>
@@ -1813,7 +1597,7 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
@@ -1822,7 +1606,7 @@
         <v>23</v>
       </c>
       <c r="D13">
-        <v>0.39</v>
+        <v>0.89</v>
       </c>
       <c r="E13" t="s">
         <v>49</v>
@@ -1833,7 +1617,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
         <v>22</v>
@@ -1842,10 +1626,10 @@
         <v>23</v>
       </c>
       <c r="D14">
-        <v>0.62</v>
+        <v>0.81</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" t="s">
         <v>26</v>
@@ -1853,7 +1637,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
@@ -1862,10 +1646,10 @@
         <v>23</v>
       </c>
       <c r="D15">
-        <v>0.43</v>
+        <v>2.12</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G15" t="s">
         <v>26</v>
@@ -1873,7 +1657,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -1882,7 +1666,7 @@
         <v>23</v>
       </c>
       <c r="D16">
-        <v>0.94</v>
+        <v>1.14</v>
       </c>
       <c r="E16" t="s">
         <v>56</v>
@@ -1893,7 +1677,7 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -1902,10 +1686,10 @@
         <v>23</v>
       </c>
       <c r="D17">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G17" t="s">
         <v>26</v>
@@ -1913,7 +1697,7 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
@@ -1922,10 +1706,10 @@
         <v>23</v>
       </c>
       <c r="D18">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G18" t="s">
         <v>26</v>
@@ -1933,7 +1717,7 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -1942,10 +1726,10 @@
         <v>23</v>
       </c>
       <c r="D19">
-        <v>0.17</v>
+        <v>0.07</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G19" t="s">
         <v>26</v>
@@ -1953,170 +1737,10 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D20">
-        <v>0.03</v>
-      </c>
-      <c r="E20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21">
-        <v>0.89</v>
-      </c>
-      <c r="E21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22">
-        <v>0.81</v>
-      </c>
-      <c r="E22" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23">
-        <v>2.12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24">
-        <v>1.14</v>
-      </c>
-      <c r="E24" t="s">
-        <v>72</v>
-      </c>
-      <c r="G24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25">
-        <v>0.88</v>
-      </c>
-      <c r="E25" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26">
-        <v>0.1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27">
-        <v>0.07</v>
-      </c>
-      <c r="E27" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
-      <c r="A28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28">
-        <v>15.19</v>
+        <v>11.54</v>
       </c>
     </row>
   </sheetData>
